--- a/reference/인쇄제작비견적서2.xlsx
+++ b/reference/인쇄제작비견적서2.xlsx
@@ -1,383 +1,164 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CHEIL\Desktop\AI TF - pioneer\reference\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E349B236-4CB8-4486-8680-5CBB153AB60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E96535EB-AC90-4FB4-A3DD-A801CF195DA4}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
-  <si>
-    <t>견 적 서</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>공급받는자</t>
-  </si>
-  <si>
-    <t>공급자</t>
-  </si>
-  <si>
-    <t>회사명</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>광고주명</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>아래와 같이 견적 합니다.
-[ 산출물: JPG, AI, 인쇄물]</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>회 사 명</t>
-  </si>
-  <si>
-    <t>㈜제일기획</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job Name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>대표이사</t>
-  </si>
-  <si>
-    <t>김종현</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Job</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>KRS00000000</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>사업자등록번호</t>
-  </si>
-  <si>
-    <t>202-81-45960</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래가격</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>(VAT 포함)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>주소</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>서울시 용산구 이태원로 222</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자/연락처</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  [견 적 내 역]</t>
-  </si>
-  <si>
-    <t>구분</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>업무내용</t>
-  </si>
-  <si>
-    <t>사전 견적</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>1차 협의 견적</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>2차 견적_0000</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>완료견적_1차</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>최종 금액</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>정가항목</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>기획료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>정가항목 제외</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>카피료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>크리에이티브 워크료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>디렉션료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sub total</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>외주항목</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>시안</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>비주얼 레이아웃</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>시안/원고용
-이미지 CG 작업</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>시안작업</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>원고작업</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI 이미지 제작 및 스탁 이미지 활용</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>연동 촬영비</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>바레이션 비용</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>제일기획 수수료</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>10% 적용</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TOTAL</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>4자리 이하 절사</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="&quot; ₩&quot;* #,##0&quot; &quot;;&quot;-₩&quot;* #,##0&quot; &quot;;&quot; ₩&quot;* &quot;- &quot;"/>
-    <numFmt numFmtId="177" formatCode="&quot; &quot;* #,##0&quot; &quot;;&quot;-&quot;* #,##0&quot; &quot;;&quot; &quot;* &quot;- &quot;"/>
+    <numFmt numFmtId="164" formatCode="&quot; ₩&quot;* #,##0&quot; &quot;;&quot;-₩&quot;* #,##0&quot; &quot;;&quot; ₩&quot;* &quot;- &quot;"/>
+    <numFmt numFmtId="165" formatCode="&quot; &quot;* #,##0&quot; &quot;;&quot;-&quot;* #,##0&quot; &quot;;&quot; &quot;* &quot;- &quot;"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="8"/>
       <sz val="24"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color indexed="8"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="major"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FFFF0000"/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <b/>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="10"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -412,12 +193,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="7" tint="0.3999755851924192"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="88">
     <border>
       <left/>
       <right/>
@@ -1237,352 +1018,835 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="8"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="170">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="5" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="30" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="39" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="41" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="42" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="45" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="46" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="51" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="3" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="3" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="54" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="57" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="58" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="58" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="52" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="47" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="15" fillId="2" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="59" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="7" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="7" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="7" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="60" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="14" fillId="6" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="6" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="63" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="64" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="80" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="81" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="71" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="84" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="85" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="10" fillId="4" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="86" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="70" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="73" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="74" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="14" fillId="3" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="3" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="2" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="7" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="6" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2 2 2" xfId="4" xr:uid="{C72A3DDD-B5F9-48FF-933D-B0764A3ABC4E}"/>
-    <cellStyle name="표준 2 3" xfId="2" xr:uid="{A4EE41A8-2FDE-4BE3-85DF-2952157A9804}"/>
-    <cellStyle name="표준 6" xfId="3" xr:uid="{E0B0C44A-15C2-4B42-9C34-70C87B5FF690}"/>
-    <cellStyle name="표준 9 2 2" xfId="1" xr:uid="{ED7BEF1C-BC3C-4354-A709-3C320D202D0B}"/>
+    <cellStyle name="표준 9 2 2" xfId="1"/>
+    <cellStyle name="표준 2 3" xfId="2"/>
+    <cellStyle name="표준 6" xfId="3"/>
+    <cellStyle name="표준 2 2 2" xfId="4"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1902,668 +2166,749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A17D6A9-2CFC-4C55-8815-3FDAE9AFC5B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.75" bestFit="1" customWidth="1"/>
+    <col width="14" bestFit="1" customWidth="1" style="105" min="1" max="1"/>
+    <col width="15.375" bestFit="1" customWidth="1" style="105" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" style="105" min="4" max="4"/>
+    <col width="14.5" bestFit="1" customWidth="1" style="105" min="5" max="5"/>
+    <col width="13.875" bestFit="1" customWidth="1" style="105" min="6" max="6"/>
+    <col width="14.875" bestFit="1" customWidth="1" style="105" min="7" max="7"/>
+    <col width="13.25" bestFit="1" customWidth="1" style="105" min="8" max="9"/>
+    <col width="16.375" bestFit="1" customWidth="1" style="105" min="10" max="10"/>
+    <col width="26.75" bestFit="1" customWidth="1" style="105" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>견 적 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="105" thickBot="1">
+      <c r="A2" s="106" t="n"/>
+      <c r="B2" s="107" t="n"/>
+      <c r="C2" s="107" t="n"/>
+      <c r="D2" s="107" t="n"/>
+      <c r="E2" s="107" t="n"/>
+      <c r="F2" s="107" t="n"/>
+      <c r="G2" s="107" t="n"/>
+      <c r="H2" s="107" t="n"/>
+      <c r="I2" s="107" t="n"/>
+      <c r="J2" s="107" t="n"/>
+      <c r="K2" s="107" t="n"/>
+    </row>
+    <row r="3" ht="17.25" customHeight="1" s="105">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>공급받는자</t>
+        </is>
+      </c>
+      <c r="B3" s="108" t="n"/>
+      <c r="C3" s="108" t="n"/>
+      <c r="D3" s="109" t="n"/>
+      <c r="E3" s="110" t="n"/>
+      <c r="F3" s="108" t="n"/>
+      <c r="G3" s="108" t="n"/>
+      <c r="H3" s="108" t="n"/>
+      <c r="I3" s="111" t="n"/>
+      <c r="J3" s="112" t="inlineStr">
+        <is>
+          <t>공급자</t>
+        </is>
+      </c>
+      <c r="K3" s="113" t="n"/>
+    </row>
+    <row r="4" ht="17.25" customHeight="1" s="105">
+      <c r="A4" s="114" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="B4" s="115" t="n"/>
+      <c r="C4" s="116" t="inlineStr">
+        <is>
+          <t>광고주명</t>
+        </is>
+      </c>
+      <c r="D4" s="117" t="n"/>
+      <c r="E4" s="118" t="inlineStr">
+        <is>
+          <t>아래와 같이 견적 합니다.
+[ 산출물: JPG, AI, 인쇄물]</t>
+        </is>
+      </c>
+      <c r="F4" s="119" t="n"/>
+      <c r="G4" s="119" t="n"/>
+      <c r="H4" s="119" t="n"/>
+      <c r="I4" s="120" t="n"/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>회 사 명</t>
+        </is>
+      </c>
+      <c r="K4" s="20" t="inlineStr">
+        <is>
+          <t>㈜광고대행사</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.25" customHeight="1" s="105">
+      <c r="A5" s="121" t="inlineStr">
+        <is>
+          <t>Job Name</t>
+        </is>
+      </c>
+      <c r="B5" s="122" t="n"/>
+      <c r="C5" s="123" t="n"/>
+      <c r="D5" s="117" t="n"/>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="19" t="inlineStr">
+        <is>
+          <t>대표이사</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>김종현</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17.25" customHeight="1" s="105">
+      <c r="A6" s="125" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="B6" s="126" t="n"/>
+      <c r="C6" s="127" t="inlineStr">
+        <is>
+          <t>KRS00000000</t>
+        </is>
+      </c>
+      <c r="D6" s="117" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="19" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>202-81-45960</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.25" customHeight="1" s="105">
+      <c r="A7" s="114" t="inlineStr">
+        <is>
+          <t>거래가격</t>
+        </is>
+      </c>
+      <c r="B7" s="115" t="n"/>
+      <c r="C7" s="128">
+        <f>I26</f>
+        <v/>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>(VAT 포함)</t>
+        </is>
+      </c>
+      <c r="I7" s="124" t="n"/>
+      <c r="J7" s="33" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>서울시 용산구 이태원로 222</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="105" thickBot="1">
+      <c r="A8" s="129" t="inlineStr">
+        <is>
+          <t>담당자/연락처</t>
+        </is>
+      </c>
+      <c r="B8" s="130" t="n"/>
+      <c r="C8" s="131" t="n"/>
+      <c r="D8" s="132" t="n"/>
+      <c r="E8" s="107" t="n"/>
+      <c r="F8" s="107" t="n"/>
+      <c r="G8" s="107" t="n"/>
+      <c r="H8" s="107" t="n"/>
+      <c r="I8" s="133" t="n"/>
+      <c r="J8" s="40" t="inlineStr">
+        <is>
+          <t>담당자/연락처</t>
+        </is>
+      </c>
+      <c r="K8" s="41" t="n"/>
+    </row>
+    <row r="9" ht="17.25" customHeight="1" s="105" thickBot="1">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  [견 적 내 역]</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n"/>
+      <c r="C9" s="43" t="n"/>
+      <c r="D9" s="43" t="n"/>
+      <c r="E9" s="43" t="n"/>
+      <c r="F9" s="43" t="n"/>
+      <c r="G9" s="43" t="n"/>
+      <c r="H9" s="43" t="n"/>
+      <c r="I9" s="43" t="n"/>
+      <c r="J9" s="44" t="n"/>
+      <c r="K9" s="45" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="134" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B10" s="135" t="n"/>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>업무내용</t>
+        </is>
+      </c>
+      <c r="D10" s="135" t="n"/>
+      <c r="E10" s="49" t="inlineStr">
+        <is>
+          <t>사전 견적</t>
+        </is>
+      </c>
+      <c r="F10" s="49" t="inlineStr">
+        <is>
+          <t>1차 협의 견적</t>
+        </is>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>2차 견적_0000</t>
+        </is>
+      </c>
+      <c r="H10" s="50" t="inlineStr">
+        <is>
+          <t>완료견적_1차</t>
+        </is>
+      </c>
+      <c r="I10" s="51" t="inlineStr">
+        <is>
+          <t>최종 금액</t>
+        </is>
+      </c>
+      <c r="J10" s="53" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="K10" s="136" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="137" t="inlineStr">
+        <is>
+          <t>정가항목</t>
+        </is>
+      </c>
+      <c r="B11" s="138" t="n"/>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>기획료</t>
+        </is>
+      </c>
+      <c r="D11" s="139" t="n"/>
+      <c r="E11" s="140" t="n">
+        <v>367000</v>
+      </c>
+      <c r="F11" s="140" t="n"/>
+      <c r="G11" s="140" t="n"/>
+      <c r="H11" s="141" t="n"/>
+      <c r="I11" s="142" t="n"/>
+      <c r="J11" s="61" t="inlineStr">
+        <is>
+          <t>정가항목 제외</t>
+        </is>
+      </c>
+      <c r="K11" s="143" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="144" t="n"/>
+      <c r="B12" s="145" t="n"/>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>카피료</t>
+        </is>
+      </c>
+      <c r="D12" s="139" t="n"/>
+      <c r="E12" s="140" t="n">
+        <v>428000</v>
+      </c>
+      <c r="F12" s="140" t="n"/>
+      <c r="G12" s="140" t="n"/>
+      <c r="H12" s="141" t="n"/>
+      <c r="I12" s="142" t="n"/>
+      <c r="J12" s="61" t="inlineStr">
+        <is>
+          <t>정가항목 제외</t>
+        </is>
+      </c>
+      <c r="K12" s="143" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="144" t="n"/>
+      <c r="B13" s="145" t="n"/>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>크리에이티브 워크료</t>
+        </is>
+      </c>
+      <c r="D13" s="139" t="n"/>
+      <c r="E13" s="140" t="n">
+        <v>408000</v>
+      </c>
+      <c r="F13" s="140" t="n"/>
+      <c r="G13" s="140" t="n"/>
+      <c r="H13" s="141" t="n"/>
+      <c r="I13" s="142" t="n"/>
+      <c r="J13" s="61" t="inlineStr">
+        <is>
+          <t>정가항목 제외</t>
+        </is>
+      </c>
+      <c r="K13" s="143" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="144" t="n"/>
+      <c r="B14" s="145" t="n"/>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>디렉션료</t>
+        </is>
+      </c>
+      <c r="D14" s="139" t="n"/>
+      <c r="E14" s="140" t="n">
+        <v>204000</v>
+      </c>
+      <c r="F14" s="140" t="n"/>
+      <c r="G14" s="140" t="n"/>
+      <c r="H14" s="141" t="n"/>
+      <c r="I14" s="142" t="n"/>
+      <c r="J14" s="61" t="inlineStr">
+        <is>
+          <t>정가항목 제외</t>
+        </is>
+      </c>
+      <c r="K14" s="143" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="146" t="inlineStr">
+        <is>
+          <t>Sub total</t>
+        </is>
+      </c>
+      <c r="B15" s="147" t="n"/>
+      <c r="C15" s="147" t="n"/>
+      <c r="D15" s="139" t="n"/>
+      <c r="E15" s="148">
+        <f>SUM(E11:E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="148">
+        <f>SUM(F11:F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="148">
+        <f>SUM(G11:G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="148">
+        <f>SUM(H11:H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="149" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
+      <c r="J15" s="70" t="n"/>
+      <c r="K15" s="143" t="n"/>
     </row>
-    <row r="2" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+    <row r="16">
+      <c r="A16" s="150" t="inlineStr">
+        <is>
+          <t>외주항목</t>
+        </is>
+      </c>
+      <c r="B16" s="151" t="n"/>
+      <c r="C16" s="56" t="inlineStr">
+        <is>
+          <t>기획료</t>
+        </is>
+      </c>
+      <c r="D16" s="139" t="n"/>
+      <c r="E16" s="140" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="F16" s="152" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G16" s="152" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H16" s="153" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="I16" s="154" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J16" s="78" t="n"/>
+      <c r="K16" s="79" t="n"/>
     </row>
-    <row r="3" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="12"/>
+    <row r="17">
+      <c r="C17" s="56" t="inlineStr">
+        <is>
+          <t>시안</t>
+        </is>
+      </c>
+      <c r="D17" s="139" t="n"/>
+      <c r="E17" s="140" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="F17" s="152" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G17" s="152" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H17" s="153" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I17" s="154" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="J17" s="79" t="n"/>
+      <c r="K17" s="143" t="n"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>7</v>
-      </c>
+    <row r="18">
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>비주얼 레이아웃</t>
+        </is>
+      </c>
+      <c r="D18" s="139" t="n"/>
+      <c r="E18" s="140" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F18" s="152" t="n">
+        <v>800000</v>
+      </c>
+      <c r="G18" s="152" t="n">
+        <v>800000</v>
+      </c>
+      <c r="H18" s="153" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I18" s="154" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J18" s="79" t="n"/>
+      <c r="K18" s="143" t="n"/>
     </row>
-    <row r="5" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>10</v>
-      </c>
+    <row r="19">
+      <c r="C19" s="155" t="inlineStr">
+        <is>
+          <t>시안/원고용
+이미지 CG 작업</t>
+        </is>
+      </c>
+      <c r="D19" s="88" t="inlineStr">
+        <is>
+          <t>시안작업</t>
+        </is>
+      </c>
+      <c r="E19" s="152" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="F19" s="152" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="G19" s="152" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="H19" s="156" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I19" s="154" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="J19" s="79" t="n"/>
+      <c r="K19" s="143" t="n"/>
     </row>
-    <row r="6" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>14</v>
-      </c>
+    <row r="20">
+      <c r="C20" s="157" t="n"/>
+      <c r="D20" s="88" t="inlineStr">
+        <is>
+          <t>원고작업</t>
+        </is>
+      </c>
+      <c r="E20" s="157" t="n"/>
+      <c r="F20" s="157" t="n"/>
+      <c r="G20" s="157" t="n"/>
+      <c r="H20" s="158" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="I20" s="154" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="J20" s="78" t="n"/>
+      <c r="K20" s="79" t="n"/>
     </row>
-    <row r="7" spans="1:11" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="31">
-        <f>I26</f>
-        <v>22880000</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>18</v>
-      </c>
+    <row r="21">
+      <c r="C21" s="155" t="inlineStr">
+        <is>
+          <t>AI 이미지 제작 및 스탁 이미지 활용</t>
+        </is>
+      </c>
+      <c r="D21" s="139" t="n"/>
+      <c r="E21" s="140" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="F21" s="152" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G21" s="152" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="H21" s="153" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="I21" s="154" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J21" s="79" t="n"/>
+      <c r="K21" s="143" t="n"/>
     </row>
-    <row r="8" spans="1:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="41"/>
+    <row r="22">
+      <c r="C22" s="56" t="inlineStr">
+        <is>
+          <t>연동 촬영비</t>
+        </is>
+      </c>
+      <c r="D22" s="139" t="n"/>
+      <c r="E22" s="140" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F22" s="152" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="G22" s="152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="153" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="I22" s="154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="61" t="n"/>
+      <c r="K22" s="143" t="n"/>
     </row>
-    <row r="9" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="45"/>
+    <row r="23">
+      <c r="A23" s="159" t="n"/>
+      <c r="B23" s="159" t="n"/>
+      <c r="C23" s="56" t="inlineStr">
+        <is>
+          <t>바레이션 비용</t>
+        </is>
+      </c>
+      <c r="D23" s="139" t="n"/>
+      <c r="E23" s="140" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="F23" s="160" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="G23" s="160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="61" t="n"/>
+      <c r="K23" s="143" t="n"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="47"/>
-      <c r="C10" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="D10" s="48"/>
-      <c r="E10" s="49" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="51" t="s">
-        <v>27</v>
-      </c>
-      <c r="J10" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="K10" s="53"/>
+    <row r="24">
+      <c r="A24" s="146" t="inlineStr">
+        <is>
+          <t>Sub total</t>
+        </is>
+      </c>
+      <c r="B24" s="147" t="n"/>
+      <c r="C24" s="147" t="n"/>
+      <c r="D24" s="139" t="n"/>
+      <c r="E24" s="148">
+        <f>SUM(E16:E23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="148">
+        <f>SUM(F16:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="148">
+        <f>SUM(G16:G23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="148">
+        <f>SUM(H16:H23)</f>
+        <v/>
+      </c>
+      <c r="I24" s="149">
+        <f>SUM(I16:I23)</f>
+        <v/>
+      </c>
+      <c r="J24" s="70" t="n"/>
+      <c r="K24" s="143" t="n"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="56"/>
-      <c r="E11" s="57">
-        <v>367000</v>
-      </c>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="K11" s="61"/>
+    <row r="25">
+      <c r="A25" s="93" t="inlineStr">
+        <is>
+          <t>광고대행사 수수료</t>
+        </is>
+      </c>
+      <c r="B25" s="147" t="n"/>
+      <c r="C25" s="147" t="n"/>
+      <c r="D25" s="139" t="n"/>
+      <c r="E25" s="163">
+        <f>E24*15%</f>
+        <v/>
+      </c>
+      <c r="F25" s="163">
+        <f>F24*15%</f>
+        <v/>
+      </c>
+      <c r="G25" s="163">
+        <f>G24*10%</f>
+        <v/>
+      </c>
+      <c r="H25" s="163">
+        <f>H24*10%</f>
+        <v/>
+      </c>
+      <c r="I25" s="164">
+        <f>I24*10%</f>
+        <v/>
+      </c>
+      <c r="J25" s="98" t="inlineStr">
+        <is>
+          <t>10% 적용</t>
+        </is>
+      </c>
+      <c r="K25" s="143" t="n"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="56" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="57">
-        <v>428000</v>
-      </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="K12" s="61"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
-      <c r="C13" s="56" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="57">
-        <v>408000</v>
-      </c>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="K13" s="61"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
-      <c r="C14" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="57">
-        <v>204000</v>
-      </c>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="K14" s="61"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="67">
-        <f>SUM(E11:E14)</f>
-        <v>1407000</v>
-      </c>
-      <c r="F15" s="67">
-        <f>SUM(F11:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="67">
-        <f>SUM(G11:G14)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="67">
-        <f>SUM(H11:H14)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="68">
-        <v>0</v>
-      </c>
-      <c r="J15" s="69"/>
-      <c r="K15" s="70"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="71" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="56" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="57">
-        <v>2000000</v>
-      </c>
-      <c r="F16" s="72">
-        <v>1500000</v>
-      </c>
-      <c r="G16" s="72">
-        <v>1000000</v>
-      </c>
-      <c r="H16" s="73">
-        <v>1000000</v>
-      </c>
-      <c r="I16" s="74">
-        <v>1000000</v>
-      </c>
-      <c r="J16" s="75"/>
-      <c r="K16" s="76"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="77"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="56" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="57">
-        <v>5000000</v>
-      </c>
-      <c r="F17" s="72">
-        <v>3000000</v>
-      </c>
-      <c r="G17" s="72">
-        <v>1500000</v>
-      </c>
-      <c r="H17" s="73">
-        <v>1500000</v>
-      </c>
-      <c r="I17" s="74">
-        <v>1500000</v>
-      </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="79"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="77"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57">
-        <v>1000000</v>
-      </c>
-      <c r="F18" s="72">
-        <v>800000</v>
-      </c>
-      <c r="G18" s="72">
-        <v>800000</v>
-      </c>
-      <c r="H18" s="73">
-        <v>800000</v>
-      </c>
-      <c r="I18" s="74">
-        <v>800000</v>
-      </c>
-      <c r="J18" s="78"/>
-      <c r="K18" s="79"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="77"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" s="81" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="82">
-        <v>70000000</v>
-      </c>
-      <c r="F19" s="82">
-        <v>50000000</v>
-      </c>
-      <c r="G19" s="82">
-        <v>20000000</v>
-      </c>
-      <c r="H19" s="83">
-        <v>15000000</v>
-      </c>
-      <c r="I19" s="74">
-        <v>9000000</v>
-      </c>
-      <c r="J19" s="78"/>
-      <c r="K19" s="79"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="77"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="84"/>
-      <c r="D20" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86">
-        <v>7000000</v>
-      </c>
-      <c r="I20" s="74">
-        <v>6500000</v>
-      </c>
-      <c r="J20" s="75"/>
-      <c r="K20" s="76"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="77"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="88"/>
-      <c r="E21" s="57">
-        <v>7000000</v>
-      </c>
-      <c r="F21" s="72">
-        <v>6000000</v>
-      </c>
-      <c r="G21" s="72">
-        <v>3500000</v>
-      </c>
-      <c r="H21" s="73">
-        <v>3000000</v>
-      </c>
-      <c r="I21" s="74">
-        <v>2000000</v>
-      </c>
-      <c r="J21" s="78"/>
-      <c r="K21" s="79"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="77"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="56" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="57">
-        <v>8000000</v>
-      </c>
-      <c r="F22" s="72">
-        <v>7000000</v>
-      </c>
-      <c r="G22" s="72">
-        <v>0</v>
-      </c>
-      <c r="H22" s="73">
-        <v>1500000</v>
-      </c>
-      <c r="I22" s="74">
-        <v>0</v>
-      </c>
-      <c r="J22" s="60"/>
-      <c r="K22" s="61"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="89"/>
-      <c r="B23" s="89"/>
-      <c r="C23" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="57">
-        <v>3000000</v>
-      </c>
-      <c r="F23" s="90">
-        <v>3000000</v>
-      </c>
-      <c r="G23" s="90">
-        <v>0</v>
-      </c>
-      <c r="H23" s="91">
-        <v>0</v>
-      </c>
-      <c r="I23" s="92">
-        <v>0</v>
-      </c>
-      <c r="J23" s="60"/>
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="65"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="67">
-        <f>SUM(E16:E23)</f>
-        <v>96000000</v>
-      </c>
-      <c r="F24" s="67">
-        <f>SUM(F16:F23)</f>
-        <v>71300000</v>
-      </c>
-      <c r="G24" s="67">
-        <f>SUM(G16:G23)</f>
-        <v>26800000</v>
-      </c>
-      <c r="H24" s="67">
-        <f>SUM(H16:H23)</f>
-        <v>29800000</v>
-      </c>
-      <c r="I24" s="68">
-        <f>SUM(I16:I23)</f>
-        <v>20800000</v>
-      </c>
-      <c r="J24" s="69"/>
-      <c r="K24" s="70"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A25" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="95">
-        <f>E24*15%</f>
-        <v>14400000</v>
-      </c>
-      <c r="F25" s="95">
-        <f>F24*15%</f>
-        <v>10695000</v>
-      </c>
-      <c r="G25" s="95">
-        <f>G24*10%</f>
-        <v>2680000</v>
-      </c>
-      <c r="H25" s="95">
-        <f>H24*10%</f>
-        <v>2980000</v>
-      </c>
-      <c r="I25" s="96">
-        <f>I24*10%</f>
-        <v>2080000</v>
-      </c>
-      <c r="J25" s="97" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="98"/>
-    </row>
-    <row r="26" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="99" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="100"/>
-      <c r="D26" s="100"/>
-      <c r="E26" s="101">
+    <row r="26" ht="17.25" customHeight="1" s="105" thickBot="1">
+      <c r="A26" s="99" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B26" s="165" t="n"/>
+      <c r="C26" s="165" t="n"/>
+      <c r="D26" s="166" t="n"/>
+      <c r="E26" s="167">
         <f>SUM(E15,E24,E25)</f>
-        <v>111807000</v>
-      </c>
-      <c r="F26" s="101">
+        <v/>
+      </c>
+      <c r="F26" s="167">
         <f>ROUNDDOWN(SUM(F15,F24,F25),-4)</f>
-        <v>81990000</v>
-      </c>
-      <c r="G26" s="101">
+        <v/>
+      </c>
+      <c r="G26" s="167">
         <f>ROUNDDOWN(SUM(G15,G24,G25),-4)</f>
-        <v>29480000</v>
-      </c>
-      <c r="H26" s="101">
+        <v/>
+      </c>
+      <c r="H26" s="167">
         <f>ROUNDDOWN(SUM(H15,H24,H25),-4)</f>
-        <v>32780000</v>
-      </c>
-      <c r="I26" s="102">
+        <v/>
+      </c>
+      <c r="I26" s="168">
         <f>ROUNDDOWN(SUM(I15,I24,I25),-4)</f>
-        <v>22880000</v>
-      </c>
-      <c r="J26" s="103" t="s">
-        <v>48</v>
-      </c>
-      <c r="K26" s="104"/>
+        <v/>
+      </c>
+      <c r="J26" s="104" t="inlineStr">
+        <is>
+          <t>4자리 이하 절사</t>
+        </is>
+      </c>
+      <c r="K26" s="169" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A16:B23"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="E4:I8"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="J26:K26"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="J22:K22"/>
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="A16:B23"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="A11:B14"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="A11:B14"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="E3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:I8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="J17:K17"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>